--- a/business/email-assets/trial-pack/3-Truck-Stock-Unbilled-Parts.xlsx
+++ b/business/email-assets/trial-pack/3-Truck-Stock-Unbilled-Parts.xlsx
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Type your own truck names in the blue cells above.</t>
   </si>
   <si>
-    <t xml:space="preserve">TradeSheets free trial pack · Blue text = your inputs · Black = formulas (don't overwrite) · Full custom setup: reply to the email you got this from.</t>
+    <t xml:space="preserve">TradeSheets free trial pack · Blue text = your inputs · Black = locked formulas (Review &gt; Unprotect Sheet to change) · Full custom setup: reply to the email you got this from.</t>
   </si>
 </sst>
 </file>
@@ -329,9 +329,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -341,21 +341,21 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -7401,6 +7401,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <mergeCells count="1">
     <mergeCell ref="A4:C4"/>
   </mergeCells>
@@ -7584,6 +7585,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
